--- a/data/batches/B01_DM_dates/Test_Validation_Report/Test_Validation_Report_B01.xlsx
+++ b/data/batches/B01_DM_dates/Test_Validation_Report/Test_Validation_Report_B01.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T19"/>
+  <dimension ref="A1:T16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -579,10 +579,10 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -677,10 +677,10 @@
         </is>
       </c>
       <c r="I3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J3" t="n">
         <v>5</v>
-      </c>
-      <c r="J3" t="n">
-        <v>10</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -775,10 +775,10 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -873,10 +873,10 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -971,10 +971,10 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SD1208</t>
+          <t>SD1209</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>FAIL - Imputation mismatch</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SD1209</t>
+          <t>SD1210</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1163,14 +1163,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1189,37 +1189,37 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL - Imputation mismatch</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>Expected injection count and P21 Found count mismatch.</t>
+          <t>Rule validation successful.</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SD1210</t>
+          <t>SD1213</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1265,10 +1265,10 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>Rule validation successful.</t>
+          <t>Expected injection count and P21 Found count mismatch.</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SD1213</t>
+          <t>SD1334</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1363,10 +1363,10 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J10" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SD1334</t>
+          <t>SD1342</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1461,10 +1461,10 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SD1335</t>
+          <t>SD1343</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1562,7 +1562,7 @@
         <v>2</v>
       </c>
       <c r="J12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SD1342</t>
+          <t>SD1349</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1653,14 +1653,14 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1679,37 +1679,37 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL - Imputation mismatch</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>Expected injection count and P21 Found count mismatch.</t>
+          <t>Rule validation successful.</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SD1343</t>
+          <t>SD1366</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1777,29 +1777,29 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="S14" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -1807,7 +1807,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>Expected injection count and P21 Found count mismatch.</t>
+          <t>Rule validation successful.</t>
         </is>
       </c>
     </row>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SD1349</t>
+          <t>SD1373</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1849,35 +1849,35 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I15" t="n">
-        <v>6</v>
-      </c>
-      <c r="J15" t="n">
-        <v>6</v>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="O15" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1900,12 +1900,12 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>FAIL - Imputation mismatch</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>Rule validation successful.</t>
+          <t>Expected injection count and P21 Found count mismatch.</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SD1366</t>
+          <t>SD1376</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1951,10 +1951,10 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2004,300 +2004,6 @@
       <c r="T16" t="inlineStr">
         <is>
           <t>Expected injection count and P21 Found count mismatch.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>B01_DM_dates</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>oncology_nsclc</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>SD1373</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Expected injection count and P21 Found count mismatch.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>B01_DM_dates</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>oncology_nsclc</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>SD1376</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>3</v>
-      </c>
-      <c r="J18" t="n">
-        <v>8</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Expected injection count and P21 Found count mismatch.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>B01_DM_dates</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>oncology_nsclc</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>SD2005</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>1</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Rule validation successful.</t>
         </is>
       </c>
     </row>
@@ -2312,7 +2018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q70"/>
+  <dimension ref="A1:Q29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2405,12 +2111,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SD2005</t>
+          <t>SD1366</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>INJ-SD2005-DM-001</t>
+          <t>INJ-SD1366-DM-001</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2425,32 +2131,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>MS200095-0022-VISION-JPN_SITE02-0037</t>
+          <t>MS200095-0022-VISION-DEU_SITE01-0004</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>DTHDTC</t>
+          <t>RFENDTC</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2024-12-11</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>2024-12-11</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -2480,12 +2186,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SD1366</t>
+          <t>SD1373</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>INJ-SD1366-DM-001</t>
+          <t>INJ-SD1373-DM-001</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2505,14 +2211,14 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>RFENDTC</t>
+          <t>RFSTDTC</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="H3" t="n">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
@@ -2555,12 +2261,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SD1373</t>
+          <t>SD0087</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>INJ-SD1373-DM-001</t>
+          <t>INJ-SD0087-DM-001</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2575,7 +2281,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MS200095-0022-VISION-FRA_SITE01-0034</t>
+          <t>MS200095-0022-VISION-ITA_SITE01-0011</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -2584,23 +2290,23 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="H4" t="n">
-        <v>22</v>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2024-01-01</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>2024-01-01</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2024-01-27</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2024-01-27</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -2635,7 +2341,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>INJ-SD0087-DM-001</t>
+          <t>INJ-SD0087-DM-002</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2650,7 +2356,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MS200095-0022-VISION-CHN_SITE01-0039</t>
+          <t>MS200095-0022-VISION-JPN_SITE02-0012</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -2659,19 +2365,19 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2024-03-21</t>
+          <t>2024-02-09</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2024-03-21</t>
+          <t>2024-02-09</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -2705,12 +2411,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SD0087</t>
+          <t>SD0088</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>INJ-SD0087-DM-002</t>
+          <t>INJ-SD0088-DM-001</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2725,28 +2431,28 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MS200095-0022-VISION-USA_SITE01-0018</t>
+          <t>MS200095-0022-VISION-USA_SITE01-0007</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>RFSTDTC</t>
+          <t>RFENDTC</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="H6" t="n">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2024-03-13</t>
+          <t>2024-12-23</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2024-03-13</t>
+          <t>2024-12-23</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -2780,12 +2486,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SD0087</t>
+          <t>SD0088</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>INJ-SD0087-DM-003</t>
+          <t>INJ-SD0088-DM-002</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2800,28 +2506,28 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MS200095-0022-VISION-JPN_SITE02-0024</t>
+          <t>MS200095-0022-VISION-CHN_SITE01-0015</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>RFSTDTC</t>
+          <t>RFENDTC</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -2855,12 +2561,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SD0087</t>
+          <t>SD1209</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>INJ-SD0087-DM-004</t>
+          <t>INJ-SD1209-DM-001</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2875,28 +2581,28 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MS200095-0022-VISION-FRA_SITE01-0046</t>
+          <t>MS200095-0022-VISION-FRA_SITE01-0003</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>RFSTDTC</t>
+          <t>RFXENDTC</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="H8" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -2930,12 +2636,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SD0087</t>
+          <t>SD1209</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>INJ-SD0087-DM-005</t>
+          <t>INJ-SD1209-DM-002</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2950,28 +2656,28 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MS200095-0022-VISION-USA_SITE02-0014</t>
+          <t>MS200095-0022-VISION-CHN_SITE01-0015</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>RFSTDTC</t>
+          <t>RFXENDTC</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2024-04-28</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2024-04-28</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -3005,12 +2711,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SD0088</t>
+          <t>SD1213</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>INJ-SD0088-DM-001</t>
+          <t>INJ-SD1213-DM-001</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3025,28 +2731,28 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MS200095-0022-VISION-ITA_SITE01-0011</t>
+          <t>MS200095-0022-VISION-USA_SITE02-0002</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>RFENDTC</t>
+          <t>RFSTDTC</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="H10" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2024-05-12</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2024-05-12</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -3080,12 +2786,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SD0088</t>
+          <t>SD1213</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>INJ-SD0088-DM-002</t>
+          <t>INJ-SD1213-DM-002</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -3105,23 +2811,23 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>RFENDTC</t>
+          <t>RFSTDTC</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="H11" t="n">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -3155,12 +2861,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SD0088</t>
+          <t>SD1342</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>INJ-SD0088-DM-003</t>
+          <t>INJ-SD1342-DM-001</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -3175,28 +2881,28 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MS200095-0022-VISION-JPN_SITE02-0024</t>
+          <t>MS200095-0022-VISION-JPN_SITE02-0017</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>RFENDTC</t>
+          <t>RFXSTDTC</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="H12" t="n">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2024-03-26</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2024-03-26</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -3230,12 +2936,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SD0088</t>
+          <t>SD1342</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>INJ-SD0088-DM-004</t>
+          <t>INJ-SD1342-DM-002</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -3250,28 +2956,28 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MS200095-0022-VISION-KOR_SITE01-0025</t>
+          <t>MS200095-0022-VISION-USA_SITE01-0007</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>RFENDTC</t>
+          <t>RFXSTDTC</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="H13" t="n">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -3305,12 +3011,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SD0088</t>
+          <t>SD1343</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>INJ-SD0088-DM-005</t>
+          <t>INJ-SD1343-DM-001</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -3325,28 +3031,28 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MS200095-0022-VISION-JPN_SITE02-0017</t>
+          <t>MS200095-0022-VISION-USA_SITE01-0018</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>RFENDTC</t>
+          <t>RFXSTDTC</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H14" t="n">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2024-03-13</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2024-03-13</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -3380,12 +3086,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SD1209</t>
+          <t>SD1343</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>INJ-SD1209-DM-001</t>
+          <t>INJ-SD1343-DM-002</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -3400,28 +3106,28 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MS200095-0022-VISION-JPN_SITE02-0012</t>
+          <t>MS200095-0022-VISION-DEU_SITE01-0009</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>RFXENDTC</t>
+          <t>RFXSTDTC</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="H15" t="n">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
+          <t>2024-02-07</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -3455,12 +3161,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SD1209</t>
+          <t>SD1376</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>INJ-SD1209-DM-002</t>
+          <t>INJ-SD1376-DM-001</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -3475,28 +3181,28 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>MS200095-0022-VISION-FRA_SITE01-0013</t>
+          <t>MS200095-0022-VISION-ITA_SITE01-0006</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>RFXENDTC</t>
+          <t>RFENDTC</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="H16" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -3530,12 +3236,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SD1209</t>
+          <t>SD1376</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>INJ-SD1209-DM-003</t>
+          <t>INJ-SD1376-DM-002</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -3550,28 +3256,28 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>MS200095-0022-VISION-DEU_SITE01-0029</t>
+          <t>MS200095-0022-VISION-JPN_SITE01-0016</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>RFXENDTC</t>
+          <t>RFENDTC</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-01-02</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-01-02</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -3605,12 +3311,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SD1209</t>
+          <t>SD0083</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>INJ-SD1209-DM-004</t>
+          <t>INJ-SD0083-DM-001</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -3625,32 +3331,40 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>MS200095-0022-VISION-KOR_SITE01-0025</t>
+          <t>MS200095-0022-VISION-USA_SITE01-0018</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>RFXENDTC</t>
+          <t>__row__</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>unique</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
+          <t>USUBJID=MS200095-0022-VISION-USA_SITE01-0018; count=1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>duplicated</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>USUBJID=MS200095-0022-VISION-USA_SITE01-0018; count=2</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -3673,19 +3387,19 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Imputation verified successfully</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SD1209</t>
+          <t>SD0083</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>INJ-SD1209-DM-005</t>
+          <t>INJ-SD0083-DM-002</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -3700,32 +3414,40 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>MS200095-0022-VISION-USA_SITE01-0041</t>
+          <t>MS200095-0022-VISION-JPN_SITE02-0020</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>RFXENDTC</t>
+          <t>__row__</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="H19" t="n">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>unique</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
+          <t>USUBJID=MS200095-0022-VISION-JPN_SITE02-0020; count=1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>duplicated</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>USUBJID=MS200095-0022-VISION-JPN_SITE02-0020; count=2</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -3748,19 +3470,19 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Imputation verified successfully</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SD1213</t>
+          <t>SD1001</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>INJ-SD1213-DM-001</t>
+          <t>INJ-SD1001-DM-001</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3775,32 +3497,40 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>MS200095-0022-VISION-DEU_SITE01-0042</t>
+          <t>MS200095-0022-VISION-ITA_SITE01-0011</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>RFSTDTC</t>
+          <t>__row__</t>
         </is>
       </c>
       <c r="G20" t="n">
+        <v>8</v>
+      </c>
+      <c r="H20" t="n">
         <v>10</v>
       </c>
-      <c r="H20" t="n">
-        <v>12</v>
-      </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2024-01-31</t>
+          <t>unique</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2024-01-31</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
+          <t>USUBJID=MS200095-0022-VISION-ITA_SITE01-0011; count=1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>duplicated</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>USUBJID=MS200095-0022-VISION-ITA_SITE01-0011; count=2</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -3823,19 +3553,19 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>Imputation verified successfully</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SD1213</t>
+          <t>SD1001</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>INJ-SD1213-DM-002</t>
+          <t>INJ-SD1001-DM-002</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3850,32 +3580,40 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>MS200095-0022-VISION-USA_SITE01-0041</t>
+          <t>MS200095-0022-VISION-USA_SITE02-0002</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>RFSTDTC</t>
+          <t>__row__</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="H21" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>unique</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
+          <t>USUBJID=MS200095-0022-VISION-USA_SITE02-0002; count=1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>duplicated</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>USUBJID=MS200095-0022-VISION-USA_SITE02-0002; count=2</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -3898,19 +3636,19 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>Imputation verified successfully</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SD1213</t>
+          <t>SD1002</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>INJ-SD1213-DM-003</t>
+          <t>INJ-SD1002-DM-001</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3925,7 +3663,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>MS200095-0022-VISION-CHN_SITE01-0043</t>
+          <t>MS200095-0022-VISION-USA_SITE02-0002</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -3933,59 +3671,41 @@
           <t>RFSTDTC</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>4</v>
-      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>6</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2024-04-19</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>2024-04-19</t>
-        </is>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>Imputation verified successfully</t>
+          <t>Row index out of range</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SD1213</t>
+          <t>SD1002</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>INJ-SD1213-DM-004</t>
+          <t>INJ-SD1002-DM-002</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -4000,7 +3720,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MS200095-0022-VISION-ITA_SITE01-0027</t>
+          <t>MS200095-0022-VISION-JPN_SITE02-0005</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4009,23 +3729,31 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="H23" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024-03-21</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
+          <t>2024-03-21</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>2024-10-28</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -4055,12 +3783,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SD1342</t>
+          <t>SD1210</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>INJ-SD1342-DM-001</t>
+          <t>INJ-SD1210-DM-001</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -4075,28 +3803,28 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>MS200095-0022-VISION-JPN_SITE02-0026</t>
+          <t>MS200095-0022-VISION-CHN_SITE01-0015</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>RFXSTDTC</t>
+          <t>RFICDTC</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -4130,12 +3858,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SD1342</t>
+          <t>SD1210</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>INJ-SD1342-DM-002</t>
+          <t>INJ-SD1210-DM-002</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -4150,67 +3878,49 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>MS200095-0022-VISION-JPN_SITE02-0019</t>
+          <t>MS200095-0022-VISION-USA_SITE01-0018</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>RFXSTDTC</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
-        <v>34</v>
-      </c>
+          <t>RFICDTC</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>36</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2024-02-24</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>2024-02-24</t>
-        </is>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>Imputation verified successfully</t>
+          <t>Row index out of range</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SD1342</t>
+          <t>SD1334</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>INJ-SD1342-DM-003</t>
+          <t>INJ-SD1334-DM-001</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -4225,32 +3935,40 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>MS200095-0022-VISION-JPN_SITE01-0032</t>
+          <t>MS200095-0022-VISION-JPN_SITE02-0020</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>RFXSTDTC</t>
+          <t>RFICDTC</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="H26" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-01-22</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
+          <t>2024-01-22</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>2024-01-08</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>2024-01-08</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -4280,12 +3998,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SD1342</t>
+          <t>SD1334</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>INJ-SD1342-DM-004</t>
+          <t>INJ-SD1334-DM-002</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4300,32 +4018,40 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>MS200095-0022-VISION-DEU_SITE01-0009</t>
+          <t>MS200095-0022-VISION-GBR_SITE01-0008</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>RFXSTDTC</t>
+          <t>RFICDTC</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2024-02-07</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
+          <t>2024-02-23</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2024-03-28</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>2024-03-28</t>
+        </is>
+      </c>
       <c r="M27" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -4355,12 +4081,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SD1343</t>
+          <t>SD1349</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>INJ-SD1343-DM-001</t>
+          <t>INJ-SD1349-DM-001</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4375,67 +4101,49 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>MS200095-0022-VISION-JPN_SITE02-0012</t>
+          <t>MS200095-0022-VISION-USA_SITE02-0002</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>RFXSTDTC</t>
-        </is>
-      </c>
-      <c r="G28" t="n">
-        <v>32</v>
-      </c>
+          <t>STUDYID</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
-        <v>34</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2024-02-09</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>2024-02-09</t>
-        </is>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>Imputation verified successfully</t>
+          <t>Row index out of range</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SD1343</t>
+          <t>SD1349</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>INJ-SD1343-DM-002</t>
+          <t>INJ-SD1349-DM-002</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4450,32 +4158,40 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>MS200095-0022-VISION-JPN_SITE02-0037</t>
+          <t>MS200095-0022-VISION-CHN_SITE01-0015</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>RFXSTDTC</t>
+          <t>STUDYID</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>MS200095-0022-VISION</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
+          <t>MS200095-0022-VISION</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>WRONG_STUDY</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>WRONG_STUDY</t>
+        </is>
+      </c>
       <c r="M29" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -4499,3175 +4215,6 @@
       <c r="Q29" t="inlineStr">
         <is>
           <t>Imputation verified successfully</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>SD1343</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>INJ-SD1343-DM-003</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>MS200095-0022-VISION-KOR_SITE01-0025</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>RFXSTDTC</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
-        <v>39</v>
-      </c>
-      <c r="H30" t="n">
-        <v>41</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2024-04-11</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>2024-04-11</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>Imputation verified successfully</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>SD1343</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>INJ-SD1343-DM-004</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>MS200095-0022-VISION-USA_SITE01-0022</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>RFXSTDTC</t>
-        </is>
-      </c>
-      <c r="G31" t="n">
-        <v>42</v>
-      </c>
-      <c r="H31" t="n">
-        <v>44</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2024-02-19</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>2024-02-19</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>Imputation verified successfully</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>SD1343</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>INJ-SD1343-DM-005</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>MS200095-0022-VISION-FRA_SITE01-0046</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>RFXSTDTC</t>
-        </is>
-      </c>
-      <c r="G32" t="n">
-        <v>21</v>
-      </c>
-      <c r="H32" t="n">
-        <v>23</v>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2024-04-11</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>2024-04-11</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>Imputation verified successfully</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>SD1376</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>INJ-SD1376-DM-001</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>MS200095-0022-VISION-CHN_SITE01-0015</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>RFENDTC</t>
-        </is>
-      </c>
-      <c r="G33" t="n">
-        <v>1</v>
-      </c>
-      <c r="H33" t="n">
-        <v>3</v>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>Imputation verified successfully</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>SD1376</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>INJ-SD1376-DM-002</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>MS200095-0022-VISION-JPN_SITE02-0026</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>RFENDTC</t>
-        </is>
-      </c>
-      <c r="G34" t="n">
-        <v>37</v>
-      </c>
-      <c r="H34" t="n">
-        <v>39</v>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2024-09-10</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>2024-09-10</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>Imputation verified successfully</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>SD1376</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>INJ-SD1376-DM-003</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>MS200095-0022-VISION-DEU_SITE01-0009</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>RFENDTC</t>
-        </is>
-      </c>
-      <c r="G35" t="n">
-        <v>7</v>
-      </c>
-      <c r="H35" t="n">
-        <v>9</v>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>Imputation verified successfully</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>SD0083</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>INJ-SD0083-DM-001</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>MS200095-0022-VISION-ESP_SITE01-0045</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>__row__</t>
-        </is>
-      </c>
-      <c r="G36" t="n">
-        <v>15</v>
-      </c>
-      <c r="H36" t="n">
-        <v>17</v>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>unique</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>USUBJID=MS200095-0022-VISION-ESP_SITE01-0045; count=1</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>duplicated</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>USUBJID=MS200095-0022-VISION-ESP_SITE01-0045; count=2</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>Duplicate row injection verified successfully</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>SD0083</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>INJ-SD0083-DM-002</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>MS200095-0022-VISION-CHN_SITE01-0039</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>__row__</t>
-        </is>
-      </c>
-      <c r="G37" t="n">
-        <v>3</v>
-      </c>
-      <c r="H37" t="n">
-        <v>5</v>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>unique</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>USUBJID=MS200095-0022-VISION-CHN_SITE01-0039; count=1</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>duplicated</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>USUBJID=MS200095-0022-VISION-CHN_SITE01-0039; count=2</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>Duplicate row injection verified successfully</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>SD0083</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>INJ-SD0083-DM-003</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>MS200095-0022-VISION-FRA_SITE01-0028</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>__row__</t>
-        </is>
-      </c>
-      <c r="G38" t="n">
-        <v>18</v>
-      </c>
-      <c r="H38" t="n">
-        <v>20</v>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>unique</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>USUBJID=MS200095-0022-VISION-FRA_SITE01-0028; count=1</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>duplicated</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>USUBJID=MS200095-0022-VISION-FRA_SITE01-0028; count=2</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>Duplicate row injection verified successfully</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>SD0083</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>INJ-SD0083-DM-004</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>MS200095-0022-VISION-USA_SITE02-0023</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>__row__</t>
-        </is>
-      </c>
-      <c r="G39" t="n">
-        <v>48</v>
-      </c>
-      <c r="H39" t="n">
-        <v>50</v>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>unique</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>USUBJID=MS200095-0022-VISION-USA_SITE02-0023; count=1</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>duplicated</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>USUBJID=MS200095-0022-VISION-USA_SITE02-0023; count=2</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>Duplicate row injection verified successfully</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>SD0083</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>INJ-SD0083-DM-005</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>MS200095-0022-VISION-USA_SITE01-0031</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>__row__</t>
-        </is>
-      </c>
-      <c r="G40" t="n">
-        <v>43</v>
-      </c>
-      <c r="H40" t="n">
-        <v>45</v>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>unique</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>USUBJID=MS200095-0022-VISION-USA_SITE01-0031; count=1</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>duplicated</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>USUBJID=MS200095-0022-VISION-USA_SITE01-0031; count=2</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>Duplicate row injection verified successfully</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>SD1001</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>INJ-SD1001-DM-001</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>MS200095-0022-VISION-GBR_SITE01-0040</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>__row__</t>
-        </is>
-      </c>
-      <c r="G41" t="n">
-        <v>24</v>
-      </c>
-      <c r="H41" t="n">
-        <v>26</v>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>unique</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>USUBJID=MS200095-0022-VISION-GBR_SITE01-0040; count=1</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>duplicated</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>USUBJID=MS200095-0022-VISION-GBR_SITE01-0040; count=2</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>Duplicate row injection verified successfully</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>SD1001</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>INJ-SD1001-DM-002</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>MS200095-0022-VISION-FRA_SITE01-0013</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>__row__</t>
-        </is>
-      </c>
-      <c r="G42" t="n">
-        <v>17</v>
-      </c>
-      <c r="H42" t="n">
-        <v>19</v>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>unique</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>USUBJID=MS200095-0022-VISION-FRA_SITE01-0013; count=1</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>duplicated</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>USUBJID=MS200095-0022-VISION-FRA_SITE01-0013; count=2</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>Duplicate row injection verified successfully</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>SD1001</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>INJ-SD1001-DM-003</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>MS200095-0022-VISION-DEU_SITE01-0004</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>__row__</t>
-        </is>
-      </c>
-      <c r="G43" t="n">
-        <v>6</v>
-      </c>
-      <c r="H43" t="n">
-        <v>8</v>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>unique</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>USUBJID=MS200095-0022-VISION-DEU_SITE01-0004; count=1</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>duplicated</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>USUBJID=MS200095-0022-VISION-DEU_SITE01-0004; count=2</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>Duplicate row injection verified successfully</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>SD1001</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>INJ-SD1001-DM-004</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>MS200095-0022-VISION-JPN_SITE02-0020</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>__row__</t>
-        </is>
-      </c>
-      <c r="G44" t="n">
-        <v>35</v>
-      </c>
-      <c r="H44" t="n">
-        <v>37</v>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>unique</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE02-0020; count=1</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>duplicated</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE02-0020; count=2</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>Duplicate row injection verified successfully</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>SD1001</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>INJ-SD1001-DM-005</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>MS200095-0022-VISION-JPN_SITE02-0010</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>__row__</t>
-        </is>
-      </c>
-      <c r="G45" t="n">
-        <v>31</v>
-      </c>
-      <c r="H45" t="n">
-        <v>33</v>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>unique</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE02-0010; count=1</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>duplicated</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE02-0010; count=2</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>Duplicate row injection verified successfully</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>SD1001</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>INJ-SD1001-DM-006</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>MS200095-0022-VISION-DEU_SITE01-0050</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>__row__</t>
-        </is>
-      </c>
-      <c r="G46" t="n">
-        <v>12</v>
-      </c>
-      <c r="H46" t="n">
-        <v>14</v>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>unique</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>USUBJID=MS200095-0022-VISION-DEU_SITE01-0050; count=1</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>duplicated</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>USUBJID=MS200095-0022-VISION-DEU_SITE01-0050; count=2</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>Duplicate row injection verified successfully</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>SD1002</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>INJ-SD1002-DM-001</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>MS200095-0022-VISION-JPN_SITE02-0020</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>RFSTDTC</t>
-        </is>
-      </c>
-      <c r="G47" t="n">
-        <v>35</v>
-      </c>
-      <c r="H47" t="n">
-        <v>37</v>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>2024-01-08</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>2024-01-08</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>Imputation verified successfully</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>SD1002</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>INJ-SD1002-DM-002</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>MS200095-0022-VISION-ESP_SITE01-0045</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>RFSTDTC</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="n">
-        <v>52</v>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>Row index out of range</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>SD1002</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>INJ-SD1002-DM-004</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>MS200095-0022-VISION-FRA_SITE01-0028</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>RFSTDTC</t>
-        </is>
-      </c>
-      <c r="G49" t="n">
-        <v>18</v>
-      </c>
-      <c r="H49" t="n">
-        <v>20</v>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>2024-03-11</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>2024-03-11</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>Imputation verified successfully</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>SD1002</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>INJ-SD1002-DM-005</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>MS200095-0022-VISION-CHN_SITE01-0047</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>RFSTDTC</t>
-        </is>
-      </c>
-      <c r="G50" t="n">
-        <v>5</v>
-      </c>
-      <c r="H50" t="n">
-        <v>7</v>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>2024-05-16</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>2024-05-16</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>Imputation verified successfully</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>SD1208</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>INJ-SD1208-DM-001</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>MS200095-0022-VISION-ESP_SITE01-0045</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>RFXSTDTC</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="n">
-        <v>52</v>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>Row index out of range</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>SD1208</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>INJ-SD1208-DM-002</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>MS200095-0022-VISION-FRA_SITE01-0003</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>RFXSTDTC</t>
-        </is>
-      </c>
-      <c r="G52" t="n">
-        <v>16</v>
-      </c>
-      <c r="H52" t="n">
-        <v>18</v>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>2024-04-18</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>2024-04-18</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>2024-08-09</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>2024-08-09</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>Imputation verified successfully</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>SD1210</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>INJ-SD1210-DM-001</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>MS200095-0022-VISION-USA_SITE02-0021</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>RFICDTC</t>
-        </is>
-      </c>
-      <c r="G53" t="n">
-        <v>47</v>
-      </c>
-      <c r="H53" t="n">
-        <v>49</v>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>2024-02-20</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>2024-02-20</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="Q53" t="inlineStr">
-        <is>
-          <t>Imputation verified successfully</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>SD1210</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>INJ-SD1210-DM-002</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>MS200095-0022-VISION-USA_SITE01-0031</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>RFICDTC</t>
-        </is>
-      </c>
-      <c r="G54" t="n">
-        <v>43</v>
-      </c>
-      <c r="H54" t="n">
-        <v>45</v>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>2024-04-14</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>2024-04-14</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="Q54" t="inlineStr">
-        <is>
-          <t>Imputation verified successfully</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>SD1210</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>INJ-SD1210-DM-003</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>MS200095-0022-VISION-JPN_SITE02-0026</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>RFICDTC</t>
-        </is>
-      </c>
-      <c r="G55" t="n">
-        <v>37</v>
-      </c>
-      <c r="H55" t="n">
-        <v>39</v>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>2024-04-01</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>2024-04-01</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>Imputation verified successfully</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>SD1210</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>INJ-SD1210-DM-004</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>MS200095-0022-VISION-FRA_SITE01-0003</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>RFICDTC</t>
-        </is>
-      </c>
-      <c r="G56" t="n">
-        <v>16</v>
-      </c>
-      <c r="H56" t="n">
-        <v>18</v>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>2024-04-03</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>2024-04-03</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>Imputation verified successfully</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>SD1210</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>INJ-SD1210-DM-005</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>MS200095-0022-VISION-ITA_SITE01-0027</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>RFICDTC</t>
-        </is>
-      </c>
-      <c r="G57" t="n">
-        <v>27</v>
-      </c>
-      <c r="H57" t="n">
-        <v>29</v>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>2024-02-07</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>2024-02-07</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="Q57" t="inlineStr">
-        <is>
-          <t>Imputation verified successfully</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>SD1210</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>INJ-SD1210-DM-006</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>MS200095-0022-VISION-USA_SITE01-0018</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>RFICDTC</t>
-        </is>
-      </c>
-      <c r="G58" t="n">
-        <v>41</v>
-      </c>
-      <c r="H58" t="n">
-        <v>43</v>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>2024-03-01</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>2024-03-01</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t>Imputation verified successfully</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>SD1334</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>INJ-SD1334-DM-001</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>MS200095-0022-VISION-ITA_SITE01-0006</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>RFICDTC</t>
-        </is>
-      </c>
-      <c r="G59" t="n">
-        <v>25</v>
-      </c>
-      <c r="H59" t="n">
-        <v>27</v>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>2024-02-07</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>2024-02-07</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>2024-03-17</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>2024-03-17</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="Q59" t="inlineStr">
-        <is>
-          <t>Imputation verified successfully</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>SD1334</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>INJ-SD1334-DM-003</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>MS200095-0022-VISION-DEU_SITE01-0009</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>RFICDTC</t>
-        </is>
-      </c>
-      <c r="G60" t="n">
-        <v>7</v>
-      </c>
-      <c r="H60" t="n">
-        <v>9</v>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>2024-01-25</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>2024-01-25</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>2024-02-14</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>2024-02-14</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="Q60" t="inlineStr">
-        <is>
-          <t>Imputation verified successfully</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>SD1334</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>INJ-SD1334-DM-004</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>MS200095-0022-VISION-KOR_SITE01-0025</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>RFICDTC</t>
-        </is>
-      </c>
-      <c r="G61" t="n">
-        <v>39</v>
-      </c>
-      <c r="H61" t="n">
-        <v>41</v>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>2024-03-28</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>2024-03-28</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>2024-04-18</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>2024-04-18</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="Q61" t="inlineStr">
-        <is>
-          <t>Imputation verified successfully</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>SD1334</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>INJ-SD1334-DM-005</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>MS200095-0022-VISION-USA_SITE01-0007</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>RFICDTC</t>
-        </is>
-      </c>
-      <c r="G62" t="n">
-        <v>40</v>
-      </c>
-      <c r="H62" t="n">
-        <v>42</v>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>2024-04-06</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>2024-04-06</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>2024-04-27</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>2024-04-27</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="Q62" t="inlineStr">
-        <is>
-          <t>Imputation verified successfully</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>SD1335</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>INJ-SD1335-DM-005</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>MS200095-0022-VISION-JPN_SITE02-0024</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>RFICDTC</t>
-        </is>
-      </c>
-      <c r="G63" t="n">
-        <v>36</v>
-      </c>
-      <c r="H63" t="n">
-        <v>38</v>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>2024-04-14</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>2024-04-14</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>2024-05-17</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>2024-05-17</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>Imputation verified successfully</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>SD1335</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>INJ-SD1335-DM-006</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>MS200095-0022-VISION-CHN_SITE01-0047</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>RFICDTC</t>
-        </is>
-      </c>
-      <c r="G64" t="n">
-        <v>5</v>
-      </c>
-      <c r="H64" t="n">
-        <v>7</v>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>2024-04-13</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>2024-04-13</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>2024-05-23</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>2024-05-23</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="Q64" t="inlineStr">
-        <is>
-          <t>Imputation verified successfully</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>SD1349</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>INJ-SD1349-DM-001</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>MS200095-0022-VISION-FRA_SITE01-0013</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>STUDYID</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="n">
-        <v>58</v>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="Q65" t="inlineStr">
-        <is>
-          <t>Row index out of range</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>SD1349</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>INJ-SD1349-DM-002</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>MS200095-0022-VISION-FRA_SITE01-0003</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>STUDYID</t>
-        </is>
-      </c>
-      <c r="G66" t="n">
-        <v>16</v>
-      </c>
-      <c r="H66" t="n">
-        <v>18</v>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>MS200095-0022-VISION</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>MS200095-0022-VISION</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>WRONG_STUDY</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>WRONG_STUDY</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="Q66" t="inlineStr">
-        <is>
-          <t>Imputation verified successfully</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>SD1349</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>INJ-SD1349-DM-003</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>MS200095-0022-VISION-DEU_SITE01-0050</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>STUDYID</t>
-        </is>
-      </c>
-      <c r="G67" t="n">
-        <v>12</v>
-      </c>
-      <c r="H67" t="n">
-        <v>14</v>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>MS200095-0022-VISION</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>MS200095-0022-VISION</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>WRONG_STUDY</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>WRONG_STUDY</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="Q67" t="inlineStr">
-        <is>
-          <t>Imputation verified successfully</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>SD1349</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>INJ-SD1349-DM-004</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>MS200095-0022-VISION-JPN_SITE02-0010</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>STUDYID</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="n">
-        <v>61</v>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="Q68" t="inlineStr">
-        <is>
-          <t>Row index out of range</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>SD1349</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>INJ-SD1349-DM-005</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>MS200095-0022-VISION-GBR_SITE01-0040</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>STUDYID</t>
-        </is>
-      </c>
-      <c r="G69" t="n">
-        <v>24</v>
-      </c>
-      <c r="H69" t="n">
-        <v>26</v>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>MS200095-0022-VISION</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>MS200095-0022-VISION</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>WRONG_STUDY</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>WRONG_STUDY</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O69" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="Q69" t="inlineStr">
-        <is>
-          <t>Imputation verified successfully</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>SD1349</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>INJ-SD1349-DM-006</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>MS200095-0022-VISION-DEU_SITE01-0050</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>STUDYID</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="n">
-        <v>62</v>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="Q70" t="inlineStr">
-        <is>
-          <t>Row index out of range</t>
         </is>
       </c>
     </row>
@@ -7798,7 +4345,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T14"/>
+  <dimension ref="A1:T11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7945,10 +4492,10 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -8043,10 +4590,10 @@
         </is>
       </c>
       <c r="I3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J3" t="n">
         <v>5</v>
-      </c>
-      <c r="J3" t="n">
-        <v>10</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -8141,10 +4688,10 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -8239,10 +4786,10 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -8308,7 +4855,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SD1209</t>
+          <t>SD1213</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -8337,10 +4884,10 @@
         </is>
       </c>
       <c r="I6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J6" t="n">
         <v>5</v>
-      </c>
-      <c r="J6" t="n">
-        <v>4</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -8406,7 +4953,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SD1213</t>
+          <t>SD1334</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -8435,10 +4982,10 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -8504,7 +5051,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SD1334</t>
+          <t>SD1342</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -8533,10 +5080,10 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -8602,7 +5149,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SD1335</t>
+          <t>SD1343</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -8634,7 +5181,7 @@
         <v>2</v>
       </c>
       <c r="J9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -8700,7 +5247,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SD1342</t>
+          <t>SD1373</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -8729,10 +5276,10 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -8798,7 +5345,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SD1343</t>
+          <t>SD1376</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -8827,10 +5374,10 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -8878,300 +5425,6 @@
         </is>
       </c>
       <c r="T11" t="inlineStr">
-        <is>
-          <t>Expected injection count and P21 Found count mismatch.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>B01_DM_dates</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>oncology_nsclc</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>SD1366</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" t="n">
-        <v>2</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Expected injection count and P21 Found count mismatch.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>B01_DM_dates</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>oncology_nsclc</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>SD1373</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" t="n">
-        <v>2</v>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Expected injection count and P21 Found count mismatch.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>B01_DM_dates</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>oncology_nsclc</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>SD1376</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>DM</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>3</v>
-      </c>
-      <c r="J14" t="n">
-        <v>8</v>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
         <is>
           <t>Expected injection count and P21 Found count mismatch.</t>
         </is>
@@ -9188,7 +5441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9250,6 +5503,192 @@
       <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Comments</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>B01_DM_dates</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>oncology_nsclc</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>SD1208</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Skipped in Error Imputation</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Rule is present in SDTM_P21 Working file for the selected batch and host generator key, but not present in Export Summary.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>B01_DM_dates</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>oncology_nsclc</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>SD1335</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Skipped in Error Imputation</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Rule is present in SDTM_P21 Working file for the selected batch and host generator key, but not present in Export Summary.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>B01_DM_dates</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>oncology_nsclc</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>SD2005</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Skipped in Error Imputation</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Rule is present in SDTM_P21 Working file for the selected batch and host generator key, but not present in Export Summary.</t>
         </is>
       </c>
     </row>
@@ -9331,10 +5770,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E2" t="n">
         <v>3</v>
@@ -9343,7 +5782,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -9352,7 +5791,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>83.33</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/data/batches/B01_DM_dates/Test_Validation_Report/Test_Validation_Report_B01.xlsx
+++ b/data/batches/B01_DM_dates/Test_Validation_Report/Test_Validation_Report_B01.xlsx
@@ -575,7 +575,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL - Imputation mismatch</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -920,7 +920,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL - Imputation mismatch</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-USA_SITE01-0018; count=1</t>
+          <t>Complete Row @ CSV Row 19; count=1</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-USA_SITE01-0018; count=2</t>
+          <t>Complete Row @ CSV Row 19; count=0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -3372,22 +3372,22 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Duplicate row injection verified successfully</t>
+          <t>Duplicate row injection mismatch</t>
         </is>
       </c>
     </row>
@@ -3435,7 +3435,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE02-0020; count=1</t>
+          <t>Complete Row @ CSV Row 17; count=1</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-JPN_SITE02-0020; count=2</t>
+          <t>Complete Row @ CSV Row 17; count=0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -3455,22 +3455,22 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Duplicate row injection verified successfully</t>
+          <t>Duplicate row injection mismatch</t>
         </is>
       </c>
     </row>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-ITA_SITE01-0011; count=1</t>
+          <t>Complete Row @ CSV Row 10; count=1</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-ITA_SITE01-0011; count=2</t>
+          <t>Complete Row @ CSV Row 10; count=0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -3538,22 +3538,22 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>Duplicate row injection verified successfully</t>
+          <t>Duplicate row injection mismatch</t>
         </is>
       </c>
     </row>
@@ -3601,7 +3601,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-USA_SITE02-0002; count=1</t>
+          <t>Complete Row @ CSV Row 20; count=1</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-USA_SITE02-0002; count=2</t>
+          <t>Complete Row @ CSV Row 20; count=0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -3621,22 +3621,22 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>Duplicate row injection verified successfully</t>
+          <t>Duplicate row injection mismatch</t>
         </is>
       </c>
     </row>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -4539,7 +4539,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL - Imputation mismatch</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -4833,7 +4833,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL - Imputation mismatch</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -5773,10 +5773,10 @@
         <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -5791,7 +5791,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>80</v>
+        <v>66.67</v>
       </c>
     </row>
   </sheetData>
